--- a/samples/odoo_contacts.xlsx
+++ b/samples/odoo_contacts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Related Company</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Job Position</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -459,22 +459,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>City</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
           <t>Country</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Salesperson</t>
         </is>
       </c>
     </row>
@@ -490,11 +480,6 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>www.abcfoods.example</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>info@abcfoods.example</t>
@@ -507,22 +492,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hamra Street</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Beirut</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Nadine Haddad</t>
         </is>
       </c>
     </row>
@@ -543,6 +518,11 @@
           <t>ABC Foods</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Procurement Manager</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>rami@abcfoods.example</t>
@@ -553,98 +533,131 @@
           <t>+961 3 555 666</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Beirut</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Beirut</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Nadine Haddad</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mount Lebanon Pharma</t>
+          <t>Mohammad Hassan</t>
         </is>
       </c>
       <c r="C4" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ABC Foods SAL</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://mlpharma.example</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>contact@mlpharma.example</t>
+          <t>m.hassan@abcfoods.example</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+961 5 777 888</t>
+          <t>01 111 223</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>+961 3 777 888</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Main Road</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Baabda</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>Lebanon</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Karim Nassar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>503</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mount Lebanon Pharma</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>contact@mlpharma.example</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+961 5 777 888</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Baabda</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>504</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Jane Doe</t>
         </is>
       </c>
-      <c r="C5" t="b">
+      <c r="C6" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>jane.doe@gmail.com</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>+961 70 123 456</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Jounieh</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Lebanon</t>
         </is>
